--- a/1_Data/Navon_2021_psyarxiv/Exp2/CodeBook_Navon_2021_psyarxiv_Exp2_Clean.xlsx
+++ b/1_Data/Navon_2021_psyarxiv/Exp2/CodeBook_Navon_2021_psyarxiv_Exp2_Clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,17 +463,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shape of the object</t>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>circle.bmp;square.bmp;triangle.bmp</t>
+          <t>self-matching</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -485,17 +485,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
+          <t>Matching task performed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>self-matching</t>
+          <t>Matching;Nomatching</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -507,17 +507,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Matching</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Matching task performed</t>
+          <t>Shape of the object</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Matching;Nomatching</t>
+          <t>circle.bmp;square.bmp;triangle.bmp</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>CorrResponse</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Participant's response</t>
+          <t>Correct response key for the trial (as designed; from raw CRESP/CorrectAnswer)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>m;z</t>
+          <t>See per-study key mapping</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -617,34 +617,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RT_ms</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reaction time in milliseconds</t>
+          <t>Participant's response</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>m;z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RT_sec</t>
+          <t>RT_ms</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reaction time in seconds</t>
+          <t>Reaction time in milliseconds</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,20 +661,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>RT_sec</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Reaction time in seconds</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Accuracy of the response</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0;1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Numerical</t>
         </is>
